--- a/data/trans_dic/IP29A_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP29A_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 meses o más (tasa de respuesta: 97,51%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>66,84%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>48,16; 82,08</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>32,13; 69,8</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44,37; 70,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>62,26%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>55,46; 68,85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51,71; 63,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55,12; 64,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>70,36%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>56,59; 73,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>60,92; 78,19</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>61,42; 73,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>63,57%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>60,53%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>58,18; 68,55</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>55,6; 65,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58,83; 65,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -774,7 +498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 meses o más (tasa de respuesta: 97,51%)</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6683956643669839</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5183303365957618</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5864437203391575</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>14256</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13301</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27558</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4816151739962525</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3212819873672347</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4436903258402243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10272; 17506</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8245; 17912</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20849; 33097</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8207716221943718</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6979946383574082</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7043357829293507</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6225820833145767</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5756393596490912</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6007406747645617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>134385</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>108115</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>242500</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5546317261290974</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.517145096108841</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5512405921830307</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>119718; 148615</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>97129; 119702</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>222519; 260442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6885051159628869</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.637328692256383</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6451881164281703</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6585563933675177</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7036012105499012</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6792585801313585</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>61519</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>55897</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>117416</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5659035871725424</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6091826396447709</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.6142334318004936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>52864; 68976</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48396; 62116</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106176; 127612</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7383780511881721</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7818846337220302</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.738243201686164</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6357029408936093</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6053233238990358</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6214308097922201</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>210160</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>177314</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>387475</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5818119974373586</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5559971157819332</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5883211579932394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>192344; 226625</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>162865; 190448</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>366830; 411175</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6855057575465572</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6501605756714314</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.659441196747299</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 97,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>14256</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>13301</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>27558</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10272</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>8245</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>20849</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17506</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>17912</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>33097</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>166</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>134385</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>108115</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>242500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>119718</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>97129</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>222519</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>148615</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>119702</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>260442</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>61519</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>55897</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>117416</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>52864</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>48396</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>106176</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>68976</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>62116</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>127612</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>210160</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>177314</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>387475</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>192344</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>162865</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>366830</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>226625</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>190448</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>411175</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>